--- a/Result/profitability/5351.xlsx
+++ b/Result/profitability/5351.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.12375</v>
+        <v>0.52</v>
       </c>
       <c r="N2" t="n">
-        <v>14.58</v>
+        <v>18.86875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.47</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.14</v>
+        <v>0.51625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.10375</v>
+        <v>18.38625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1075</v>
+        <v>0.57</v>
       </c>
       <c r="N4" t="n">
-        <v>12.65625</v>
+        <v>17.85125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.11625</v>
+        <v>0.5725</v>
       </c>
       <c r="N5" t="n">
-        <v>11.76125</v>
+        <v>17.40375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07250000000000001</v>
+        <v>0.5824999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>11.60125</v>
+        <v>16.53875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>-0.3</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.05625000000000001</v>
+        <v>0.5187499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>11.5325</v>
+        <v>15.1975</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03750000000000001</v>
+        <v>0.32875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.34375</v>
+        <v>13.2825</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.37</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.09624999999999999</v>
+        <v>-0.09624999999999995</v>
       </c>
       <c r="N10" t="n">
         <v>12.05125</v>
@@ -1772,7 +1772,7 @@
         <v>0.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0.035</v>
+        <v>0.03500000000000003</v>
       </c>
       <c r="N11" t="n">
         <v>14.14875</v>
@@ -1899,7 +1899,7 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06625</v>
+        <v>0.06625000000000003</v>
       </c>
       <c r="N12" t="n">
         <v>14.93625</v>
@@ -2026,7 +2026,7 @@
         <v>-0.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.08750000000000005</v>
       </c>
       <c r="N13" t="n">
         <v>14.3225</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5351</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4899</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2343</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2555</v>
+      </c>
+      <c r="F75" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1725</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>35.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1733</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1580</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5475</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.558510638297872</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4231923601637106</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.871428571428571</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>6.43019943019943</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
